--- a/www/ig/fhir/core/StructureDefinition-fr-core-slot.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-slot.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="295">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Slot</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Slot|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -418,7 +418,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -431,14 +431,14 @@
     <t>Slot.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -460,6 +460,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot|2.2.0</t>
+  </si>
+  <si>
     <t>Slot.meta.security</t>
   </si>
   <si>
@@ -482,7 +485,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -506,7 +509,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -549,7 +552,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -672,7 +675,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -703,7 +706,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -776,7 +779,7 @@
     <t>Slot.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -804,7 +807,7 @@
     <t>A broad categorization of the service that is to be performed during this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -819,7 +822,7 @@
     <t>The type of appointments that can be booked into this slot (ideally this would be an identifiable service - which is at a location, rather than the location itself). If provided then this overrides the value provided on the availability resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>Slot.specialty</t>
@@ -831,7 +834,7 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>Slot.appointmentType</t>
@@ -843,13 +846,13 @@
     <t>The style of appointment or patient that may be booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0276|3.0.0</t>
   </si>
   <si>
     <t>Slot.schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule|2.2.0)
 </t>
   </si>
   <si>
@@ -868,7 +871,7 @@
     <t>busy | free | busy-unavailable | busy-tentative | entered-in-error.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/slotstatus</t>
+    <t>http://hl7.org/fhir/ValueSet/slotstatus|4.0.1</t>
   </si>
   <si>
     <t>FREEBUSY;FBTYPE=(freeBusyType):19980314T233000Z/19980315T003000Z If the freeBusyType is BUSY, then this value can be excluded</t>
@@ -1236,17 +1239,17 @@
   <dimension ref="A1:AM38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.1796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.89453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="23.4453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.2265625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.2578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="63.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1255,25 +1258,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.3984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="32.79296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="28.2890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="99.8984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="123.62109375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="86.17578125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="106.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2438,7 +2441,7 @@
         <v>77</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>77</v>
@@ -2503,10 +2506,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2529,16 +2532,16 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2564,13 +2567,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2588,7 +2591,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2614,10 +2617,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2640,16 +2643,16 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2675,13 +2678,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -2699,7 +2702,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2725,10 +2728,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2754,13 +2757,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2810,7 +2813,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2836,10 +2839,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2862,16 +2865,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2897,13 +2900,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -2921,7 +2924,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2947,14 +2950,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2973,16 +2976,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3032,7 +3035,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3047,7 +3050,7 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
@@ -3058,14 +3061,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3084,16 +3087,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3143,7 +3146,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3158,7 +3161,7 @@
         <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
@@ -3169,10 +3172,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3201,7 +3204,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3254,7 +3257,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3269,7 +3272,7 @@
         <v>115</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>77</v>
@@ -3280,10 +3283,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3309,16 +3312,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3367,7 +3370,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3382,7 +3385,7 @@
         <v>115</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
@@ -3393,10 +3396,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3419,13 +3422,13 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3476,7 +3479,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3497,15 +3500,15 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3611,10 +3614,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3722,10 +3725,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3748,19 +3751,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3785,11 +3788,11 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -3807,7 +3810,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3822,7 +3825,7 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
@@ -3833,10 +3836,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3859,19 +3862,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -3896,13 +3899,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -3920,7 +3923,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3935,7 +3938,7 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>77</v>
@@ -3946,10 +3949,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3975,16 +3978,16 @@
         <v>128</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -3997,7 +4000,7 @@
         <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4033,7 +4036,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4048,7 +4051,7 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>77</v>
@@ -4059,10 +4062,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4088,13 +4091,13 @@
         <v>101</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4108,7 +4111,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4144,7 +4147,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4159,7 +4162,7 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
@@ -4170,10 +4173,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4196,13 +4199,13 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4253,7 +4256,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4268,7 +4271,7 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
@@ -4279,10 +4282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4305,16 +4308,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4364,7 +4367,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4379,7 +4382,7 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>77</v>
@@ -4390,10 +4393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4416,13 +4419,13 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4449,11 +4452,11 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4471,7 +4474,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4492,15 +4495,15 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4523,13 +4526,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4556,11 +4559,11 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -4578,7 +4581,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4599,15 +4602,15 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4630,13 +4633,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4663,11 +4666,11 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -4685,7 +4688,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4706,15 +4709,15 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4737,13 +4740,13 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4770,11 +4773,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4792,7 +4795,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4813,15 +4816,15 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4844,13 +4847,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4901,7 +4904,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>87</v>
@@ -4927,10 +4930,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4953,13 +4956,13 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4986,11 +4989,11 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5008,7 +5011,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5026,7 +5029,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5034,10 +5037,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5063,10 +5066,10 @@
         <v>122</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5117,7 +5120,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5135,18 +5138,18 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5172,10 +5175,10 @@
         <v>122</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5226,7 +5229,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>87</v>
@@ -5244,18 +5247,18 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5278,13 +5281,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5292,7 +5295,7 @@
         <v>77</v>
       </c>
       <c r="Q37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R37" t="s" s="2">
         <v>77</v>
@@ -5337,7 +5340,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5363,10 +5366,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5392,10 +5395,10 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5446,7 +5449,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-slot.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-slot.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="294">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Slot|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Slot</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -418,7 +418,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -431,14 +431,14 @@
     <t>Slot.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -460,9 +460,6 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot|2.2.0</t>
-  </si>
-  <si>
     <t>Slot.meta.security</t>
   </si>
   <si>
@@ -485,7 +482,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -509,7 +506,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -552,7 +549,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -675,7 +672,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -706,7 +703,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -779,7 +776,7 @@
     <t>Slot.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -807,7 +804,7 @@
     <t>A broad categorization of the service that is to be performed during this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -822,7 +819,7 @@
     <t>The type of appointments that can be booked into this slot (ideally this would be an identifiable service - which is at a location, rather than the location itself). If provided then this overrides the value provided on the availability resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type</t>
   </si>
   <si>
     <t>Slot.specialty</t>
@@ -834,7 +831,7 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
   </si>
   <si>
     <t>Slot.appointmentType</t>
@@ -846,13 +843,13 @@
     <t>The style of appointment or patient that may be booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
   </si>
   <si>
     <t>Slot.schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule)
 </t>
   </si>
   <si>
@@ -871,7 +868,7 @@
     <t>busy | free | busy-unavailable | busy-tentative | entered-in-error.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/slotstatus|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/slotstatus</t>
   </si>
   <si>
     <t>FREEBUSY;FBTYPE=(freeBusyType):19980314T233000Z/19980315T003000Z If the freeBusyType is BUSY, then this value can be excluded</t>
@@ -1239,17 +1236,17 @@
   <dimension ref="A1:AM38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="23.4453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.2265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.2578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.1796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="22.28515625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.89453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="63.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="68.421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1258,25 +1255,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.2890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.3984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.453125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="86.17578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="106.63671875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="99.8984375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.62109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2441,7 +2438,7 @@
         <v>77</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>77</v>
@@ -2506,10 +2503,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2532,16 +2529,16 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2567,31 +2564,31 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2617,10 +2614,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2643,16 +2640,16 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2678,31 +2675,31 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2728,10 +2725,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2757,13 +2754,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2813,7 +2810,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2839,10 +2836,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2865,16 +2862,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2900,31 +2897,31 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2950,14 +2947,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2976,16 +2973,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3035,7 +3032,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3050,7 +3047,7 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
@@ -3061,14 +3058,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3087,16 +3084,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3146,7 +3143,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3161,7 +3158,7 @@
         <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
@@ -3172,10 +3169,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3204,7 +3201,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3257,7 +3254,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3272,7 +3269,7 @@
         <v>115</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>77</v>
@@ -3283,10 +3280,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3312,16 +3309,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3370,7 +3367,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3385,7 +3382,7 @@
         <v>115</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
@@ -3396,10 +3393,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3422,13 +3419,13 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3479,7 +3476,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3500,15 +3497,15 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3614,10 +3611,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3725,10 +3722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3751,19 +3748,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3788,29 +3785,29 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3825,7 +3822,7 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
@@ -3836,10 +3833,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3862,19 +3859,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -3899,31 +3896,31 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="Z24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3938,7 +3935,7 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>77</v>
@@ -3949,10 +3946,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3978,16 +3975,16 @@
         <v>128</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4000,43 +3997,43 @@
         <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4051,7 +4048,7 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>77</v>
@@ -4062,10 +4059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4091,13 +4088,13 @@
         <v>101</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4111,43 +4108,43 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4162,7 +4159,7 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
@@ -4173,10 +4170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4199,13 +4196,13 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4256,7 +4253,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4271,7 +4268,7 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
@@ -4282,10 +4279,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4308,16 +4305,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4367,7 +4364,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4382,7 +4379,7 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>77</v>
@@ -4393,10 +4390,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4419,13 +4416,13 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4452,11 +4449,11 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4474,7 +4471,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4495,15 +4492,15 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4526,13 +4523,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4559,11 +4556,11 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -4581,7 +4578,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4602,15 +4599,15 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4633,13 +4630,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4666,11 +4663,11 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -4688,7 +4685,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4709,15 +4706,15 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4740,13 +4737,13 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4773,11 +4770,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4795,7 +4792,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4816,15 +4813,15 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4847,13 +4844,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4904,7 +4901,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>87</v>
@@ -4930,10 +4927,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4956,13 +4953,13 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4989,11 +4986,11 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5011,7 +5008,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5029,7 +5026,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5037,10 +5034,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5066,10 +5063,10 @@
         <v>122</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5120,7 +5117,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5138,18 +5135,18 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5175,10 +5172,10 @@
         <v>122</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5229,7 +5226,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>87</v>
@@ -5247,18 +5244,18 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5281,13 +5278,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5295,7 +5292,7 @@
         <v>77</v>
       </c>
       <c r="Q37" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R37" t="s" s="2">
         <v>77</v>
@@ -5340,7 +5337,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5366,10 +5363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5395,10 +5392,10 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5449,7 +5446,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-slot.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-slot.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="295">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Slot</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Slot|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -418,7 +418,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -431,14 +431,14 @@
     <t>Slot.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -460,6 +460,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot|2.2.0</t>
+  </si>
+  <si>
     <t>Slot.meta.security</t>
   </si>
   <si>
@@ -482,7 +485,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -506,7 +509,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -549,7 +552,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -672,7 +675,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -703,7 +706,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -776,7 +779,7 @@
     <t>Slot.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -804,7 +807,7 @@
     <t>A broad categorization of the service that is to be performed during this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -819,7 +822,7 @@
     <t>The type of appointments that can be booked into this slot (ideally this would be an identifiable service - which is at a location, rather than the location itself). If provided then this overrides the value provided on the availability resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>Slot.specialty</t>
@@ -831,7 +834,7 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>Slot.appointmentType</t>
@@ -843,13 +846,13 @@
     <t>The style of appointment or patient that may be booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0276|3.0.0</t>
   </si>
   <si>
     <t>Slot.schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule|2.2.0)
 </t>
   </si>
   <si>
@@ -868,7 +871,7 @@
     <t>busy | free | busy-unavailable | busy-tentative | entered-in-error.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/slotstatus</t>
+    <t>http://hl7.org/fhir/ValueSet/slotstatus|4.0.1</t>
   </si>
   <si>
     <t>FREEBUSY;FBTYPE=(freeBusyType):19980314T233000Z/19980315T003000Z If the freeBusyType is BUSY, then this value can be excluded</t>
@@ -1236,17 +1239,17 @@
   <dimension ref="A1:AM38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.1796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.89453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="23.4453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.2265625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.2578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="63.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1255,25 +1258,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.3984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="32.79296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="28.2890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="99.8984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="123.62109375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="86.17578125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="106.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2438,7 +2441,7 @@
         <v>77</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>77</v>
@@ -2503,10 +2506,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2529,16 +2532,16 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2564,13 +2567,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2588,7 +2591,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2614,10 +2617,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2640,16 +2643,16 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2675,13 +2678,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -2699,7 +2702,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2725,10 +2728,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2754,13 +2757,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2810,7 +2813,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2836,10 +2839,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2862,16 +2865,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2897,13 +2900,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -2921,7 +2924,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2947,14 +2950,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2973,16 +2976,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3032,7 +3035,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3047,7 +3050,7 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
@@ -3058,14 +3061,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3084,16 +3087,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3143,7 +3146,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3158,7 +3161,7 @@
         <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
@@ -3169,10 +3172,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3201,7 +3204,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3254,7 +3257,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3269,7 +3272,7 @@
         <v>115</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>77</v>
@@ -3280,10 +3283,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3309,16 +3312,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3367,7 +3370,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3382,7 +3385,7 @@
         <v>115</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
@@ -3393,10 +3396,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3419,13 +3422,13 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3476,7 +3479,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3497,15 +3500,15 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3611,10 +3614,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3722,10 +3725,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3748,19 +3751,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3785,11 +3788,11 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -3807,7 +3810,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3822,7 +3825,7 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
@@ -3833,10 +3836,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3859,19 +3862,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -3896,13 +3899,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -3920,7 +3923,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3935,7 +3938,7 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>77</v>
@@ -3946,10 +3949,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3975,16 +3978,16 @@
         <v>128</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -3997,7 +4000,7 @@
         <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4033,7 +4036,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4048,7 +4051,7 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>77</v>
@@ -4059,10 +4062,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4088,13 +4091,13 @@
         <v>101</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4108,7 +4111,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4144,7 +4147,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4159,7 +4162,7 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
@@ -4170,10 +4173,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4196,13 +4199,13 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4253,7 +4256,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4268,7 +4271,7 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
@@ -4279,10 +4282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4305,16 +4308,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4364,7 +4367,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4379,7 +4382,7 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>77</v>
@@ -4390,10 +4393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4416,13 +4419,13 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4449,11 +4452,11 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4471,7 +4474,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4492,15 +4495,15 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4523,13 +4526,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4556,11 +4559,11 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -4578,7 +4581,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4599,15 +4602,15 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4630,13 +4633,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4663,11 +4666,11 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -4685,7 +4688,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4706,15 +4709,15 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4737,13 +4740,13 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4770,11 +4773,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4792,7 +4795,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4813,15 +4816,15 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4844,13 +4847,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4901,7 +4904,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>87</v>
@@ -4927,10 +4930,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4953,13 +4956,13 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4986,11 +4989,11 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5008,7 +5011,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5026,7 +5029,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5034,10 +5037,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5063,10 +5066,10 @@
         <v>122</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5117,7 +5120,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5135,18 +5138,18 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5172,10 +5175,10 @@
         <v>122</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5226,7 +5229,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>87</v>
@@ -5244,18 +5247,18 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5278,13 +5281,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5292,7 +5295,7 @@
         <v>77</v>
       </c>
       <c r="Q37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R37" t="s" s="2">
         <v>77</v>
@@ -5337,7 +5340,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5363,10 +5366,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5392,10 +5395,10 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5446,7 +5449,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
